--- a/public/downloads/TML_Master_Definition_Template.xlsx
+++ b/public/downloads/TML_Master_Definition_Template.xlsx
@@ -449,7 +449,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v xml:space="preserve">  Logical Group  One of: Vehicle Data | Dealer Network | Service Operations | Parts, Claims &amp; Support</v>
+        <v xml:space="preserve">  Logical Group  One of: Vehicle Data | Dealer Network | Service Operations | Parts, Claims &amp; Support | Electronic Quality Check</v>
       </c>
     </row>
     <row r="11">

--- a/public/downloads/TML_Master_Definition_Template.xlsx
+++ b/public/downloads/TML_Master_Definition_Template.xlsx
@@ -449,7 +449,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v xml:space="preserve">  Logical Group  One of: Vehicle Data | Dealer Network | Service Operations | Parts, Claims &amp; Support | Electronic Quality Check</v>
+        <v xml:space="preserve">  Logical Group  One of: Vehicle Data | Dealer Network | Service Operations | Parts, Claims &amp; Support | Electronic Quality Check | Bodyshop</v>
       </c>
     </row>
     <row r="11">

--- a/public/downloads/TML_Master_Definition_Template.xlsx
+++ b/public/downloads/TML_Master_Definition_Template.xlsx
@@ -444,7 +444,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v xml:space="preserve">  Module Code    One of: appointment, reception, security, jc_creation, jc_tracking, spd, thd, eqc, claim, bodyshop, ira, dealer_network</v>
+        <v xml:space="preserve">  Module Code    One of: appointment, reception, receptionist, security, jc_creation, bodyshop, jc_tracking, eqc, thd, spd, claim, customer_journey</v>
       </c>
     </row>
     <row r="10">

--- a/public/downloads/TML_Master_Definition_Template.xlsx
+++ b/public/downloads/TML_Master_Definition_Template.xlsx
@@ -449,7 +449,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v xml:space="preserve">  Logical Group  One of: Vehicle Data | Dealer Network | Service Operations | Parts, Claims &amp; Support | Electronic Quality Check | Bodyshop</v>
+        <v xml:space="preserve">  Logical Group  One of: Common Masters | Vehicle Data | Dealer Network | Service Operations | Parts, Claims &amp; Support | Electronic Quality Check | Bodyshop</v>
       </c>
     </row>
     <row r="11">

--- a/public/downloads/TML_Master_Definition_Template.xlsx
+++ b/public/downloads/TML_Master_Definition_Template.xlsx
@@ -816,7 +816,7 @@
         <v>Y</v>
       </c>
       <c r="F4" t="str">
-        <v>PV, EV, CV</v>
+        <v>PV, EV</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -846,7 +846,7 @@
         <v>Vehicle Segment</v>
       </c>
       <c r="P4" t="str">
-        <v>PV=Passenger Vehicle; EV=Electric Vehicle; CV=Commercial Vehicle</v>
+        <v>PV=Passenger Vehicle; EV=Electric Vehicle</v>
       </c>
       <c r="Q4" t="str">
         <v/>

--- a/public/downloads/TML_Master_Definition_Template.xlsx
+++ b/public/downloads/TML_Master_Definition_Template.xlsx
@@ -6,7 +6,8 @@
     <sheet name="README" sheetId="1" r:id="rId1"/>
     <sheet name="Masters" sheetId="2" r:id="rId2"/>
     <sheet name="Fields" sheetId="3" r:id="rId3"/>
-    <sheet name="tyre_brand_master" sheetId="4" r:id="rId4"/>
+    <sheet name="Rules" sheetId="4" r:id="rId4"/>
+    <sheet name="tyre_brand_master" sheetId="5" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
@@ -400,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A34"/>
+  <dimension ref="A1:A48"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -534,47 +535,117 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>RECORDS — one sheet per master, named exactly as its Master ID</v>
+        <v>SHEET "Rules" (optional) — business rules, one row per rule; checked on every save and upload, no coding</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v xml:space="preserve">  Row 1 = column headers: "id" plus each Field Key (the Field Label also works).</v>
+        <v xml:space="preserve">  Rule Type      required_if | unique | not_greater | allowed_if | exists_in | range | pattern</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v xml:space="preserve">  "id" is optional; blank ids are generated. Booleans: Y/N. Dates: YYYY-MM-DD.</v>
+        <v xml:space="preserve">    required_if  A field must be filled when another field has a certain value. e.g. Plant Name is required when Role is Plant.</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v xml:space="preserve">  For an existing record, blank cells are left unchanged — you only need id + the columns you are filling in.</v>
+        <v xml:space="preserve">    unique       No two active rows may have the same values in these fields. e.g. PPL + Complaint Code must be unique.</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v/>
+        <v xml:space="preserve">    not_greater  One number or date must not be greater than another. e.g. From Km must not be greater than To Km.</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Adding things you missed later: add the new master/field/rows to a workbook and import it again with</v>
+        <v xml:space="preserve">    allowed_if   While a condition holds, a field may only take some values. e.g. When BU is EV, Powertrain may only be EV.</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>"Update existing masters" selected. Existing fields are never changed or removed by an import;</v>
+        <v xml:space="preserve">    exists_in    The value must be an active value of a field in another master. e.g. Dealer Code must exist in the Dealer Registry.</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
+        <v xml:space="preserve">    range        A number must be within a minimum and / or maximum. e.g. Warranty Months between 0 and 120.</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v xml:space="preserve">    pattern      A text must follow a fixed pattern. e.g. Dealer Code: 3 capitals, a hyphen and 3 digits.</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v xml:space="preserve">  Field / When Field / Other Field   field key or label; Fields (No duplicates) and value lists are comma separated</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v xml:space="preserve">  When Values    condition values (blank = "is filled"); Allowed Values: values allowed while the condition holds</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v xml:space="preserve">  Min / Max      for "range"; Format: a pattern for "pattern"; Other Master / Other Master Field: for "exists_in"</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v xml:space="preserve">  Severity       error (row refused) or warning (saved, user warned); Message: optional own wording; Enabled: Y / N</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>RECORDS — one sheet per master, named exactly as its Master ID</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v xml:space="preserve">  Row 1 = column headers: "id" plus each Field Key (the Field Label also works).</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v xml:space="preserve">  "id" is optional; blank ids are generated. Booleans: Y/N. Dates: YYYY-MM-DD.</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v xml:space="preserve">  For an existing record, blank cells are left unchanged — you only need id + the columns you are filling in.</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>Adding things you missed later: add the new master/field/rows to a workbook and import it again with</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>"Update existing masters" selected. Existing fields are never changed or removed by an import;</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
         <v>records are matched by id (existing ids are updated, new ids are added).</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A34"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A48"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1020,6 +1091,217 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P4"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Master ID</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Rule Type</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Field</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Fields (No duplicates)</v>
+      </c>
+      <c r="E1" t="str">
+        <v>When Field</v>
+      </c>
+      <c r="F1" t="str">
+        <v>When Values</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Other Field</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Allowed Values</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Min</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Max</v>
+      </c>
+      <c r="K1" t="str">
+        <v>Format</v>
+      </c>
+      <c r="L1" t="str">
+        <v>Other Master</v>
+      </c>
+      <c r="M1" t="str">
+        <v>Other Master Field</v>
+      </c>
+      <c r="N1" t="str">
+        <v>Severity</v>
+      </c>
+      <c r="O1" t="str">
+        <v>Message</v>
+      </c>
+      <c r="P1" t="str">
+        <v>Enabled</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>tyre_brand_master</v>
+      </c>
+      <c r="B2" t="str">
+        <v>unique</v>
+      </c>
+      <c r="C2" t="str">
+        <v/>
+      </c>
+      <c r="D2" t="str">
+        <v>brand_code</v>
+      </c>
+      <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2" t="str">
+        <v/>
+      </c>
+      <c r="G2" t="str">
+        <v/>
+      </c>
+      <c r="H2" t="str">
+        <v/>
+      </c>
+      <c r="I2" t="str">
+        <v/>
+      </c>
+      <c r="J2" t="str">
+        <v/>
+      </c>
+      <c r="K2" t="str">
+        <v/>
+      </c>
+      <c r="L2" t="str">
+        <v/>
+      </c>
+      <c r="M2" t="str">
+        <v/>
+      </c>
+      <c r="N2" t="str">
+        <v>error</v>
+      </c>
+      <c r="O2" t="str">
+        <v/>
+      </c>
+      <c r="P2" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>tyre_brand_master</v>
+      </c>
+      <c r="B3" t="str">
+        <v>required_if</v>
+      </c>
+      <c r="C3" t="str">
+        <v>effective_from</v>
+      </c>
+      <c r="D3" t="str">
+        <v/>
+      </c>
+      <c r="E3" t="str">
+        <v>active</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Y</v>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v/>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v/>
+      </c>
+      <c r="M3" t="str">
+        <v/>
+      </c>
+      <c r="N3" t="str">
+        <v>error</v>
+      </c>
+      <c r="O3" t="str">
+        <v/>
+      </c>
+      <c r="P3" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>tyre_brand_master</v>
+      </c>
+      <c r="B4" t="str">
+        <v>range</v>
+      </c>
+      <c r="C4" t="str">
+        <v>warranty_months</v>
+      </c>
+      <c r="D4" t="str">
+        <v/>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4">
+        <v>12</v>
+      </c>
+      <c r="J4">
+        <v>72</v>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v/>
+      </c>
+      <c r="M4" t="str">
+        <v/>
+      </c>
+      <c r="N4" t="str">
+        <v>warning</v>
+      </c>
+      <c r="O4" t="str">
+        <v>Warranty is usually 12 to 72 months — please double-check.</v>
+      </c>
+      <c r="P4" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:P4"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G3"/>
   <sheetData>
     <row r="1">

--- a/public/downloads/TML_Master_Definition_Template.xlsx
+++ b/public/downloads/TML_Master_Definition_Template.xlsx
@@ -445,7 +445,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v xml:space="preserve">  Module Code    One of: appointment, reception, receptionist, security, jc_creation, bodyshop, jc_tracking, eqc, thd, spd, claim, customer_journey</v>
+        <v xml:space="preserve">  Module Code    One of: appointment, reception, receptionist, security, jc_creation, bodyshop, jc_tracking, eqc, thd, spd, claim, customer_journey, common</v>
       </c>
     </row>
     <row r="10">
